--- a/class2/excel/interest.xlsx
+++ b/class2/excel/interest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\snguyen4\Dropbox\git\math110\class2\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282F107A-3D98-45CC-8D2A-90CAC7122BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCF2F72-5AAE-4D70-B971-A9DBB7D6A969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{669B2E44-DD9B-4BC8-B268-B6503CAF7CE3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Principal</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>n =</t>
+  </si>
+  <si>
+    <t>Continuous Compound</t>
+  </si>
+  <si>
+    <t>A (Continuous Compound)</t>
+  </si>
+  <si>
+    <t>Number e =</t>
   </si>
 </sst>
 </file>
@@ -101,13 +110,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -325,97 +338,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>115.99999999999999</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>124</c:v>
+                  <c:v>1150</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>132</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>140</c:v>
+                  <c:v>1250</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>148</c:v>
+                  <c:v>1300</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>156</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>164</c:v>
+                  <c:v>1400</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>172</c:v>
+                  <c:v>1450</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>180</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>188</c:v>
+                  <c:v>1550</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>196</c:v>
+                  <c:v>1600</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>204</c:v>
+                  <c:v>1650</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>212</c:v>
+                  <c:v>1700.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>220.00000000000003</c:v>
+                  <c:v>1750</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>228.00000000000003</c:v>
+                  <c:v>1800</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>236.00000000000003</c:v>
+                  <c:v>1850</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>244</c:v>
+                  <c:v>1900</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>252</c:v>
+                  <c:v>1950.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>260</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>268</c:v>
+                  <c:v>2050</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>276</c:v>
+                  <c:v>2100</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>284</c:v>
+                  <c:v>2150.0000000000005</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>292</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>300</c:v>
+                  <c:v>2250</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>308</c:v>
+                  <c:v>2300</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>316</c:v>
+                  <c:v>2350</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>324</c:v>
+                  <c:v>2400.0000000000005</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>332</c:v>
+                  <c:v>2450</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>340</c:v>
+                  <c:v>2500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -572,97 +585,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>116.64000000000001</c:v>
+                  <c:v>1102.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>125.97120000000001</c:v>
+                  <c:v>1157.6250000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>136.04889600000004</c:v>
+                  <c:v>1215.5062499999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>146.93280768000002</c:v>
+                  <c:v>1276.2815625000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>158.68743229440005</c:v>
+                  <c:v>1340.095640625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>171.38242687795207</c:v>
+                  <c:v>1407.1004226562502</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>185.09302102818822</c:v>
+                  <c:v>1477.4554437890627</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>199.90046271044329</c:v>
+                  <c:v>1551.3282159785158</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>215.89249972727879</c:v>
+                  <c:v>1628.8946267774415</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>233.16389970546106</c:v>
+                  <c:v>1710.3393581163139</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>251.81701168189798</c:v>
+                  <c:v>1795.8563260221292</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>271.96237261644984</c:v>
+                  <c:v>1885.649142323236</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>293.71936242576584</c:v>
+                  <c:v>1979.9315994393974</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>317.21691141982717</c:v>
+                  <c:v>2078.9281794113681</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>342.59426433341332</c:v>
+                  <c:v>2182.8745883819361</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>370.00180548008638</c:v>
+                  <c:v>2292.0183178010329</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>399.60194991849335</c:v>
+                  <c:v>2406.6192336910849</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>431.57010591197286</c:v>
+                  <c:v>2526.9501953756389</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>466.09571438493066</c:v>
+                  <c:v>2653.2977051444209</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>503.38337153572513</c:v>
+                  <c:v>2785.962590401642</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>543.65404125858322</c:v>
+                  <c:v>2925.2607199217236</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>587.14636455926984</c:v>
+                  <c:v>3071.5237559178104</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>634.11807372401142</c:v>
+                  <c:v>3225.0999437137007</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>684.84751962193252</c:v>
+                  <c:v>3386.3549408993858</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>739.63532119168701</c:v>
+                  <c:v>3555.6726879443554</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>798.80614688702201</c:v>
+                  <c:v>3733.4563223415735</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>862.71063863798383</c:v>
+                  <c:v>3920.1291384586516</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>931.72748972902252</c:v>
+                  <c:v>4116.1355953815846</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1006.2656889073445</c:v>
+                  <c:v>4321.9423751506629</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -819,97 +832,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108.32870745300023</c:v>
+                  <c:v>1050.625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>117.35108858437707</c:v>
+                  <c:v>1103.8128906249997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>127.124917445481</c:v>
+                  <c:v>1159.6934182128903</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>137.71277991938317</c:v>
+                  <c:v>1218.4028975099177</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>149.18247448426268</c:v>
+                  <c:v>1280.084544196357</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>161.60744635520359</c:v>
+                  <c:v>1344.8888242462974</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>175.06725778439287</c:v>
+                  <c:v>1412.9738209737661</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>189.64809753124467</c:v>
+                  <c:v>1484.5056206605632</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>205.44333276480256</c:v>
+                  <c:v>1559.6587177065039</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>222.55410693247683</c:v>
+                  <c:v>1638.6164402903955</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>241.08998742352017</c:v>
+                  <c:v>1721.5713975800966</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>261.16966717450026</c:v>
+                  <c:v>1808.725949582589</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>282.92172470943876</c:v>
+                  <c:v>1900.292700780207</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>306.48544748147049</c:v>
+                  <c:v>1996.4950187572049</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>332.01172378822099</c:v>
+                  <c:v>2097.5675790817882</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>359.66400897220507</c:v>
+                  <c:v>2203.7569377728037</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>389.61937209323258</c:v>
+                  <c:v>2315.3221327475517</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>422.06962977509443</c:v>
+                  <c:v>2432.5353157178965</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>457.22257448702305</c:v>
+                  <c:v>2555.6824160761139</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>495.3033051251233</c:v>
+                  <c:v>2685.0638383899673</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>536.55566841403618</c:v>
+                  <c:v>2820.9951952084589</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>581.24382035873111</c:v>
+                  <c:v>2963.8080769658868</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>629.65391774505224</c:v>
+                  <c:v>3113.8508608622842</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>682.09595052039219</c:v>
+                  <c:v>3271.4895606934379</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>738.9057267879972</c:v>
+                  <c:v>3437.1087197035426</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>800.44702312563402</c:v>
+                  <c:v>3611.1123486385345</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>867.11391399801755</c:v>
+                  <c:v>3793.9249112883595</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>939.33329517917252</c:v>
+                  <c:v>3985.992359922333</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1017.567617343273</c:v>
+                  <c:v>4187.7832231434004</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1102.3178473282592</c:v>
+                  <c:v>4399.7897488150338</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -918,6 +931,253 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-D3C6-464C-A8F1-A69FC7F1EBD1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A (Continuous Compound)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1051.2710963760242</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1105.1709180756477</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1161.834242728283</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1221.4027581601699</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1284.0254166877414</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1349.8588075760031</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1419.0675485932572</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1491.8246976412704</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1568.312185490169</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1648.7212707001281</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1733.2530178673953</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1822.118800390509</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1915.5408290138962</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2013.7527074704767</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2117.0000166126747</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2225.5409284924681</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2339.6468519259911</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2459.60311115695</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2585.7096593158462</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2718.2818284590453</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2857.6511180631637</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3004.1660239464336</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3158.1929096897679</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3320.1169227365481</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3490.3429574618413</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3669.2966676192445</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3857.4255306969744</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4055.1999668446756</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4263.1145151688188</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4481.6890703380641</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D3C6-464C-A8F1-A69FC7F1EBD1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1787,16 +2047,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>257680</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>34428</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>226150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>86980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>564281</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>43179</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>28254</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>95731</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1865,22 +2125,69 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>73573</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>166941</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>294290</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>123969</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78B8CA8E-B593-1283-EA63-5E4423FE4F72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="73573" y="3293769"/>
+          <a:ext cx="1713186" cy="508821"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8813DB84-07D2-4728-95C1-8CAFC962F85E}" name="Table1" displayName="Table1" ref="E1:H32" totalsRowShown="0">
-  <autoFilter ref="E1:H32" xr:uid="{8813DB84-07D2-4728-95C1-8CAFC962F85E}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8813DB84-07D2-4728-95C1-8CAFC962F85E}" name="Table1" displayName="Table1" ref="E1:I32" totalsRowShown="0">
+  <autoFilter ref="E1:I32" xr:uid="{8813DB84-07D2-4728-95C1-8CAFC962F85E}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{7F12E790-36C6-4DA6-B511-C4758982255C}" name="Time (t)"/>
-    <tableColumn id="2" xr3:uid="{56F4C9FB-4ECA-48C1-B00C-C27CB2C852E0}" name="A - Simple" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{56F4C9FB-4ECA-48C1-B00C-C27CB2C852E0}" name="A - Simple" dataDxfId="3">
       <calculatedColumnFormula>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8EB4C9EB-672C-444E-A773-3034C2E82FC5}" name="A - Compound" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{8EB4C9EB-672C-444E-A773-3034C2E82FC5}" name="A - Compound" dataDxfId="2">
       <calculatedColumnFormula>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1193A931-3565-4869-A18A-8F75F8BC0ADF}" name="A (n times)" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{1193A931-3565-4869-A18A-8F75F8BC0ADF}" name="A (n times)" dataDxfId="1">
       <calculatedColumnFormula>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{19E57053-C249-447E-9711-64DEA2C125D0}" name="A (Continuous Compound)" dataDxfId="0">
+      <calculatedColumnFormula>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2204,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53F01C82-1FC3-4297-B913-A6D073008EC9}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -2212,14 +2519,15 @@
     <col min="6" max="6" width="9.44140625" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -2233,48 +2541,59 @@
       <c r="H1" t="s">
         <v>6</v>
       </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G2">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H2">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>100</v>
+        <v>1000</v>
+      </c>
+      <c r="I2" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>108</v>
+        <v>1050</v>
       </c>
       <c r="G3">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>108</v>
+        <v>1050</v>
       </c>
       <c r="H3">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>108.32870745300023</v>
+        <v>1050.625</v>
+      </c>
+      <c r="I3" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1051.2710963760242</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2283,52 +2602,64 @@
       </c>
       <c r="F4">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>115.99999999999999</v>
+        <v>1100</v>
       </c>
       <c r="G4">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>116.64000000000001</v>
+        <v>1102.5</v>
       </c>
       <c r="H4">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>117.35108858437707</v>
+        <v>1103.8128906249997</v>
+      </c>
+      <c r="I4" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1105.1709180756477</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>124</v>
+        <v>1150</v>
       </c>
       <c r="G5">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>125.97120000000001</v>
+        <v>1157.6250000000002</v>
       </c>
       <c r="H5">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>127.124917445481</v>
+        <v>1159.6934182128903</v>
+      </c>
+      <c r="I5" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1161.834242728283</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>132</v>
+        <v>1200</v>
       </c>
       <c r="G6">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>136.04889600000004</v>
+        <v>1215.5062499999999</v>
       </c>
       <c r="H6">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>137.71277991938317</v>
+        <v>1218.4028975099177</v>
+      </c>
+      <c r="I6" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1221.4027581601699</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2337,69 +2668,85 @@
       </c>
       <c r="F7">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>140</v>
+        <v>1250</v>
       </c>
       <c r="G7">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>146.93280768000002</v>
+        <v>1276.2815625000001</v>
       </c>
       <c r="H7">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>149.18247448426268</v>
+        <v>1280.084544196357</v>
+      </c>
+      <c r="I7" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1284.0254166877414</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E8">
         <v>6</v>
       </c>
       <c r="F8">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>148</v>
+        <v>1300</v>
       </c>
       <c r="G8">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>158.68743229440005</v>
+        <v>1340.095640625</v>
       </c>
       <c r="H8">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>161.60744635520359</v>
+        <v>1344.8888242462974</v>
+      </c>
+      <c r="I8" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1349.8588075760031</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E9">
         <v>7</v>
       </c>
       <c r="F9">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>156</v>
+        <v>1350</v>
       </c>
       <c r="G9">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>171.38242687795207</v>
+        <v>1407.1004226562502</v>
       </c>
       <c r="H9">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>175.06725778439287</v>
+        <v>1412.9738209737661</v>
+      </c>
+      <c r="I9" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1419.0675485932572</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E10">
         <v>8</v>
       </c>
       <c r="F10">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>164</v>
+        <v>1400</v>
       </c>
       <c r="G10">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>185.09302102818822</v>
+        <v>1477.4554437890627</v>
       </c>
       <c r="H10">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>189.64809753124467</v>
+        <v>1484.5056206605632</v>
+      </c>
+      <c r="I10" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1491.8246976412704</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2408,378 +2755,476 @@
       </c>
       <c r="F11">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>172</v>
+        <v>1450</v>
       </c>
       <c r="G11">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>199.90046271044329</v>
+        <v>1551.3282159785158</v>
       </c>
       <c r="H11">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>205.44333276480256</v>
+        <v>1559.6587177065039</v>
+      </c>
+      <c r="I11" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1568.312185490169</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E12">
         <v>10</v>
       </c>
       <c r="F12">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>180</v>
+        <v>1500</v>
       </c>
       <c r="G12">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>215.89249972727879</v>
+        <v>1628.8946267774415</v>
       </c>
       <c r="H12">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>222.55410693247683</v>
+        <v>1638.6164402903955</v>
+      </c>
+      <c r="I12" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1648.7212707001281</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E13">
         <v>11</v>
       </c>
       <c r="F13">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>188</v>
+        <v>1550</v>
       </c>
       <c r="G13">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>233.16389970546106</v>
+        <v>1710.3393581163139</v>
       </c>
       <c r="H13">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>241.08998742352017</v>
+        <v>1721.5713975800966</v>
+      </c>
+      <c r="I13" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1733.2530178673953</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E14">
         <v>12</v>
       </c>
       <c r="F14">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>196</v>
+        <v>1600</v>
       </c>
       <c r="G14">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>251.81701168189798</v>
+        <v>1795.8563260221292</v>
       </c>
       <c r="H14">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>261.16966717450026</v>
+        <v>1808.725949582589</v>
+      </c>
+      <c r="I14" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1822.118800390509</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15">
-        <v>100000000</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>13</v>
       </c>
       <c r="F15">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>204</v>
+        <v>1650</v>
       </c>
       <c r="G15">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>271.96237261644984</v>
+        <v>1885.649142323236</v>
       </c>
       <c r="H15">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>282.92172470943876</v>
+        <v>1900.292700780207</v>
+      </c>
+      <c r="I15" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>1915.5408290138962</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E16">
         <v>14</v>
       </c>
       <c r="F16">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>212</v>
+        <v>1700.0000000000002</v>
       </c>
       <c r="G16">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>293.71936242576584</v>
+        <v>1979.9315994393974</v>
       </c>
       <c r="H16">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>306.48544748147049</v>
+        <v>1996.4950187572049</v>
+      </c>
+      <c r="I16" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2013.7527074704767</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E17">
         <v>15</v>
       </c>
       <c r="F17">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>220.00000000000003</v>
+        <v>1750</v>
       </c>
       <c r="G17">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>317.21691141982717</v>
+        <v>2078.9281794113681</v>
       </c>
       <c r="H17">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>332.01172378822099</v>
+        <v>2097.5675790817882</v>
+      </c>
+      <c r="I17" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2117.0000166126747</v>
       </c>
     </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
       <c r="E18">
         <v>16</v>
       </c>
       <c r="F18">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>228.00000000000003</v>
+        <v>1800</v>
       </c>
       <c r="G18">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>342.59426433341332</v>
+        <v>2182.8745883819361</v>
       </c>
       <c r="H18">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>359.66400897220507</v>
+        <v>2203.7569377728037</v>
+      </c>
+      <c r="I18" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2225.5409284924681</v>
       </c>
     </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E19">
         <v>17</v>
       </c>
       <c r="F19">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>236.00000000000003</v>
+        <v>1850</v>
       </c>
       <c r="G19">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>370.00180548008638</v>
+        <v>2292.0183178010329</v>
       </c>
       <c r="H19">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>389.61937209323258</v>
+        <v>2315.3221327475517</v>
+      </c>
+      <c r="I19" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2339.6468519259911</v>
       </c>
     </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E20">
         <v>18</v>
       </c>
       <c r="F20">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>244</v>
+        <v>1900</v>
       </c>
       <c r="G20">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>399.60194991849335</v>
+        <v>2406.6192336910849</v>
       </c>
       <c r="H20">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>422.06962977509443</v>
+        <v>2432.5353157178965</v>
+      </c>
+      <c r="I20" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2459.60311115695</v>
       </c>
     </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E21">
         <v>19</v>
       </c>
       <c r="F21">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>252</v>
+        <v>1950.0000000000002</v>
       </c>
       <c r="G21">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>431.57010591197286</v>
+        <v>2526.9501953756389</v>
       </c>
       <c r="H21">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>457.22257448702305</v>
+        <v>2555.6824160761139</v>
+      </c>
+      <c r="I21" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2585.7096593158462</v>
       </c>
     </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <f>EXP(1)</f>
+        <v>2.7182818284590451</v>
+      </c>
       <c r="E22">
         <v>20</v>
       </c>
       <c r="F22">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>260</v>
+        <v>2000</v>
       </c>
       <c r="G22">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>466.09571438493066</v>
+        <v>2653.2977051444209</v>
       </c>
       <c r="H22">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>495.3033051251233</v>
+        <v>2685.0638383899673</v>
+      </c>
+      <c r="I22" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2718.2818284590453</v>
       </c>
     </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E23">
         <v>21</v>
       </c>
       <c r="F23">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>268</v>
+        <v>2050</v>
       </c>
       <c r="G23">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>503.38337153572513</v>
+        <v>2785.962590401642</v>
       </c>
       <c r="H23">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>536.55566841403618</v>
+        <v>2820.9951952084589</v>
+      </c>
+      <c r="I23" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>2857.6511180631637</v>
       </c>
     </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E24">
         <v>22</v>
       </c>
       <c r="F24">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>276</v>
+        <v>2100</v>
       </c>
       <c r="G24">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>543.65404125858322</v>
+        <v>2925.2607199217236</v>
       </c>
       <c r="H24">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>581.24382035873111</v>
+        <v>2963.8080769658868</v>
+      </c>
+      <c r="I24" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>3004.1660239464336</v>
       </c>
     </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E25">
         <v>23</v>
       </c>
       <c r="F25">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>284</v>
+        <v>2150.0000000000005</v>
       </c>
       <c r="G25">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>587.14636455926984</v>
+        <v>3071.5237559178104</v>
       </c>
       <c r="H25">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>629.65391774505224</v>
+        <v>3113.8508608622842</v>
+      </c>
+      <c r="I25" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>3158.1929096897679</v>
       </c>
     </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E26">
         <v>24</v>
       </c>
       <c r="F26">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>292</v>
+        <v>2200</v>
       </c>
       <c r="G26">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>634.11807372401142</v>
+        <v>3225.0999437137007</v>
       </c>
       <c r="H26">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>682.09595052039219</v>
+        <v>3271.4895606934379</v>
+      </c>
+      <c r="I26" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>3320.1169227365481</v>
       </c>
     </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E27">
         <v>25</v>
       </c>
       <c r="F27">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>300</v>
+        <v>2250</v>
       </c>
       <c r="G27">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>684.84751962193252</v>
+        <v>3386.3549408993858</v>
       </c>
       <c r="H27">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>738.9057267879972</v>
+        <v>3437.1087197035426</v>
+      </c>
+      <c r="I27" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>3490.3429574618413</v>
       </c>
     </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E28">
         <v>26</v>
       </c>
       <c r="F28">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>308</v>
+        <v>2300</v>
       </c>
       <c r="G28">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>739.63532119168701</v>
+        <v>3555.6726879443554</v>
       </c>
       <c r="H28">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>800.44702312563402</v>
+        <v>3611.1123486385345</v>
+      </c>
+      <c r="I28" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>3669.2966676192445</v>
       </c>
     </row>
-    <row r="29" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E29">
         <v>27</v>
       </c>
       <c r="F29">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>316</v>
+        <v>2350</v>
       </c>
       <c r="G29">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>798.80614688702201</v>
+        <v>3733.4563223415735</v>
       </c>
       <c r="H29">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>867.11391399801755</v>
+        <v>3793.9249112883595</v>
+      </c>
+      <c r="I29" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>3857.4255306969744</v>
       </c>
     </row>
-    <row r="30" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E30">
         <v>28</v>
       </c>
       <c r="F30">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>324</v>
+        <v>2400.0000000000005</v>
       </c>
       <c r="G30">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>862.71063863798383</v>
+        <v>3920.1291384586516</v>
       </c>
       <c r="H30">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>939.33329517917252</v>
+        <v>3985.992359922333</v>
+      </c>
+      <c r="I30" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>4055.1999668446756</v>
       </c>
     </row>
-    <row r="31" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E31">
         <v>29</v>
       </c>
       <c r="F31">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>332</v>
+        <v>2450</v>
       </c>
       <c r="G31">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>931.72748972902252</v>
+        <v>4116.1355953815846</v>
       </c>
       <c r="H31">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>1017.567617343273</v>
+        <v>4187.7832231434004</v>
+      </c>
+      <c r="I31" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>4263.1145151688188</v>
       </c>
     </row>
-    <row r="32" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E32">
         <v>30</v>
       </c>
       <c r="F32">
         <f>$B$1*(1+$B$2*Table1[[#This Row],[Time (t)]])</f>
-        <v>340</v>
+        <v>2500</v>
       </c>
       <c r="G32">
         <f>$B$1*(1+$B$2)^Table1[[#This Row],[Time (t)]]</f>
-        <v>1006.2656889073445</v>
+        <v>4321.9423751506629</v>
       </c>
       <c r="H32">
         <f>$B$1*(1+$B$2/$B$15)^($B$15*Table1[[#This Row],[Time (t)]])</f>
-        <v>1102.3178473282592</v>
+        <v>4399.7897488150338</v>
+      </c>
+      <c r="I32" s="1">
+        <f>$B$1*($B$22)^($B$2*Table1[[#This Row],[Time (t)]])</f>
+        <v>4481.6890703380641</v>
       </c>
     </row>
   </sheetData>
